--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0233.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0233.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Chuyện Kể Từ Núi Firmament</t>
+          <t>Những Câu Chuyện từ Núi Firmament</t>
         </is>
       </c>
     </row>
@@ -27490,7 +27490,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Cung cấp 1.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 1.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -27620,7 +27620,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Cung cấp 1.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 1.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -27685,7 +27685,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Cung cấp 3.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 3.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -27750,7 +27750,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Cung cấp 3.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 3.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -27815,7 +27815,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Cung cấp 8.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 8.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -27880,7 +27880,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Cung cấp 8.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 8.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -27945,7 +27945,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Cung cấp 20.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 20.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -28010,7 +28010,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Cung cấp 20.000 Kinh nghiệm Weapons.</t>
+          <t>Cung cấp 20.000 Kinh nghiệm Vũ khí.</t>
         </is>
       </c>
     </row>
